--- a/astro-site/public/dl/bakery-checklist-templates/07-bakery-cleaning-maintenance-schedule.xlsx
+++ b/astro-site/public/dl/bakery-checklist-templates/07-bakery-cleaning-maintenance-schedule.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Deep clean the ovens (ash, grease)</t>
+          <t>Deep clean the ovens (carbon, grease)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
